--- a/sheets/국악이꽃피는나무/검수/사랑.xlsx
+++ b/sheets/국악이꽃피는나무/검수/사랑.xlsx
@@ -2737,17 +2737,17 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
